--- a/knowledge/06_实验数据/首轮试验方案.xlsx
+++ b/knowledge/06_实验数据/首轮试验方案.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,50 +443,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>LLC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mLL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LD</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>POE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
@@ -499,10 +504,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -511,28 +516,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
         <v>36</v>
       </c>
-      <c r="G2" t="n">
-        <v>19</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>7446</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>茂金属置换</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7989</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>国产同类 LLDPE 替代</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -543,40 +551,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>7937</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>POE 补韧</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7988</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>国产同类 LLDPE 替代</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -587,10 +598,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -599,28 +610,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7409</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>再生线性料</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7994</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>国产同类 LLDPE 替代</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -631,40 +645,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>7891</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>温和版</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7670</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>同类替代 + 再生料上调</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -675,10 +692,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -687,28 +704,31 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>7869</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>二级料试探</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7942</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>同类替代 + 再生料上调</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -719,40 +739,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>7501</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>去 HDPE</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8125</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>茂金属置换</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -763,40 +786,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>8121</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>去 HDPE</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7894</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>再生线性料</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -807,7 +833,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -816,31 +842,34 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7111</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>再生线性料</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8385</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>POE 补韧</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -851,40 +880,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>58</v>
-      </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>7281</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>POE 补韧</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7648</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>国产同类 LLDPE 替代</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -895,40 +927,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" t="n">
         <v>18</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
-        <v>7451</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>再生线性料</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7955</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>国产同类 LLDPE 替代</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -939,10 +974,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -951,28 +986,31 @@
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>7965</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>POE 补韧</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7945</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>同类替代 + 再生料上调</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -983,40 +1021,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7641</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>MDPE 替代</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8299</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>温和版</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1027,40 +1068,43 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>41</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>20</v>
       </c>
-      <c r="C14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7334</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>茂金属置换</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8435</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>去 HDPE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1071,40 +1115,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>7584</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>茂金属置换</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7920</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>再生线性料</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1115,40 +1162,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>7541</v>
-      </c>
-      <c r="J16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8283</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>去 HDPE</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1159,40 +1209,43 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I17" t="n">
-        <v>7965</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>去 HDPE</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7977</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>再生线性料</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1203,40 +1256,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>52</v>
+      </c>
+      <c r="H18" t="n">
         <v>12</v>
       </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>54</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4</v>
-      </c>
       <c r="I18" t="n">
-        <v>7729</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>POE 补韧</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7793</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>再生线性料</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1247,7 +1303,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1256,31 +1312,34 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>7485</v>
-      </c>
-      <c r="J19" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8396</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>POE 补韧</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1291,7 +1350,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1303,28 +1362,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>7106</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>再生线性料</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8045</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>MDPE 替代</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1335,40 +1397,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>8119</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>去 HDPE</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8401</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>POE 补韧</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1379,40 +1444,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>7643</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>茂金属置换</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8559</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>去 HDPE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1423,40 +1491,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>7921</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>温和版</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7991</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>茂金属置换</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1467,40 +1538,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7925</v>
-      </c>
-      <c r="J24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8416</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>POE 补韧</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>D-最优</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1511,40 +1585,936 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>22</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8558</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>去 HDPE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D-最优</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R1-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7428.4</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R1-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>38</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>41</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7578.639999999999</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R1-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>38</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7570.358</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R1-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>36</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7567.918</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R1-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>18</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8035</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R1-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>38</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7569.64</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R1-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>38</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7582.139999999999</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>R1-32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>33</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7609.74</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>R1-33</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>40</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7571.700000000001</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>R1-34</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>59</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8188.02</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R1-35</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
         <v>39</v>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7961</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>POE 补韧</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>D-最优</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>45</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>8212.42</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>R1-36</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>49</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>8200.219999999999</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>R1-37</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>22</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7921.5</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>R1-38</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>20</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>47</v>
+      </c>
+      <c r="H39" t="n">
+        <v>16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>8017</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>R1-39</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>8187.5</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>R1-40</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8152</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R1-41</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>35</v>
+      </c>
+      <c r="H42" t="n">
+        <v>20</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7582.956</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>R1-42</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>35</v>
+      </c>
+      <c r="H43" t="n">
+        <v>20</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7566.698</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R1-43</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>37</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="H44" t="n">
+        <v>20</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7584.360000000001</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>优先配方</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Top 20 优先</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1559,7 +2529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,37 +2566,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mLL</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LD</t>
+          <t>mLL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1636,89 +2606,106 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>LD</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POE</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>POE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>constraint_violations</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1766,7 +2753,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>先测现用膜 base（sample_id 以 S0 开头），五项各 ≥5 条，记录单次测量值</t>
+          <t>先测现用膜 base（sample_id 以 S0 开头），四项各 ≥5 条，记录单次测量值</t>
         </is>
       </c>
     </row>

--- a/knowledge/06_实验数据/首轮试验方案.xlsx
+++ b/knowledge/06_实验数据/首轮试验方案.xlsx
@@ -507,32 +507,32 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>7989</v>
+        <v>7906</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>国产同类 LLDPE 替代</t>
+          <t>同类替代 + 再生料上调</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -551,31 +551,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7988</v>
+        <v>7961</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -613,20 +613,20 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>7994</v>
+        <v>8385</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>国产同类 LLDPE 替代</t>
+          <t>POE 补韧</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -657,23 +657,23 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7670</v>
+        <v>7981</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>同类替代 + 再生料上调</t>
+          <t>国产同类 LLDPE 替代</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -707,20 +707,20 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7942</v>
+        <v>7988</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>同类替代 + 再生料上调</t>
+          <t>国产同类 LLDPE 替代</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -739,35 +739,35 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>8125</v>
+        <v>7574</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>茂金属置换</t>
+          <t>国产同类 LLDPE 替代</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -795,26 +795,26 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>7894</v>
+        <v>8385</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>再生线性料</t>
+          <t>POE 补韧</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -842,26 +842,26 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>8385</v>
+        <v>7980</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>POE 补韧</t>
+          <t>再生线性料</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -880,35 +880,35 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7648</v>
+        <v>8357</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>国产同类 LLDPE 替代</t>
+          <t>POE 补韧</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -927,35 +927,35 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>36</v>
+      </c>
+      <c r="H11" t="n">
         <v>20</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>45</v>
-      </c>
-      <c r="H11" t="n">
-        <v>18</v>
-      </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>7955</v>
+        <v>8161</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>国产同类 LLDPE 替代</t>
+          <t>茂金属置换</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -974,31 +974,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7945</v>
+        <v>7946</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1045,11 +1045,11 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>8299</v>
+        <v>8576</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>温和版</t>
+          <t>去 HDPE</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1068,35 +1068,35 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>8435</v>
+        <v>7949</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>去 HDPE</t>
+          <t>同类替代 + 再生料上调</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1115,35 +1115,35 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7920</v>
+        <v>7921</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>再生线性料</t>
+          <t>国产同类 LLDPE 替代</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1162,35 +1162,35 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" t="n">
         <v>17</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>58</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>8283</v>
+        <v>7688</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>去 HDPE</t>
+          <t>再生线性料</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1209,35 +1209,35 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>45</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>34</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>38</v>
-      </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7977</v>
+        <v>8435</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>再生线性料</t>
+          <t>去 HDPE</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1256,13 +1256,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1271,20 +1271,20 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7793</v>
+        <v>8311</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>再生线性料</t>
+          <t>去 HDPE</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>8396</v>
+        <v>8456</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1350,35 +1350,35 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8045</v>
+        <v>7862</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>MDPE 替代</t>
+          <t>茂金属置换</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>8401</v>
+        <v>8065</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1444,22 +1444,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1468,11 +1468,11 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>8559</v>
+        <v>8303</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>去 HDPE</t>
+          <t>温和版</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>28</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>44</v>
+      </c>
+      <c r="H23" t="n">
         <v>20</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="n">
-        <v>45</v>
-      </c>
-      <c r="H23" t="n">
-        <v>14</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
-        <v>7991</v>
+        <v>7977</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>茂金属置换</t>
+          <t>再生线性料</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1538,23 +1538,23 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>18</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>21</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>19</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>59</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -1562,11 +1562,11 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>8416</v>
+        <v>8536</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>POE 补韧</t>
+          <t>去 HDPE</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>22</v>
@@ -1609,11 +1609,11 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>8558</v>
+        <v>8358</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>去 HDPE</t>
+          <t>POE 补韧</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2569,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -2654,7 +2654,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="D7" t="n">
         <v>43</v>
@@ -2674,7 +2674,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -2691,7 +2691,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
